--- a/nriss-patch-1/ig/StructureDefinition-fr-service-request-document.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-service-request-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T11:47:07+00:00</t>
+    <t>2026-04-20T11:58:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
